--- a/data/trans_orig/P6601-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6601-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a ruido tan alto que tiene que levantar la voz para hablar con otras personas en su trabajo en 2007</t>
+          <t>Población según la exposición a ruido tan alto que tiene que levantar la voz para hablar con otras personas en su trabajo en 2007 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>142978</t>
+          <t>143120</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>182324</t>
+          <t>182137</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>95930</t>
+          <t>96027</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>118520</t>
+          <t>119370</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>247630</t>
+          <t>245235</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>294496</t>
+          <t>295069</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,8%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76398</t>
+          <t>77021</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>110270</t>
+          <t>110362</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17737</t>
+          <t>17801</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36888</t>
+          <t>37650</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97122</t>
+          <t>100054</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>138171</t>
+          <t>141176</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>71084</t>
+          <t>71804</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>104365</t>
+          <t>105862</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>6420</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>21390</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>82026</t>
+          <t>82188</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>119167</t>
+          <t>119766</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25333</t>
+          <t>25352</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48306</t>
+          <t>49187</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12868</t>
+          <t>12265</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31301</t>
+          <t>30480</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56389</t>
+          <t>53908</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>467648</t>
+          <t>464226</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>536083</t>
+          <t>535363</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>414845</t>
+          <t>415390</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>458675</t>
+          <t>457190</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>896275</t>
+          <t>895169</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>976395</t>
+          <t>977059</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,29%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>239481</t>
+          <t>241956</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>297261</t>
+          <t>299002</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80778</t>
+          <t>82638</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119734</t>
+          <t>120363</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>336819</t>
+          <t>337625</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>405174</t>
+          <t>408542</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>241815</t>
+          <t>243327</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>298485</t>
+          <t>300254</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21178</t>
+          <t>20291</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42597</t>
+          <t>40859</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>269129</t>
+          <t>268678</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>331418</t>
+          <t>330047</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>71171</t>
+          <t>69403</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>107051</t>
+          <t>106903</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24252</t>
+          <t>23796</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>85499</t>
+          <t>83384</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>124812</t>
+          <t>123083</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>264329</t>
+          <t>266815</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>303747</t>
+          <t>304324</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>219804</t>
+          <t>218901</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>247408</t>
+          <t>245787</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>497130</t>
+          <t>494427</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>543058</t>
+          <t>542351</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,98%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71679</t>
+          <t>71687</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>106979</t>
+          <t>105444</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31045</t>
+          <t>31228</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54898</t>
+          <t>56340</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>110631</t>
+          <t>109297</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>150817</t>
+          <t>153035</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12599</t>
+          <t>12394</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29712</t>
+          <t>31225</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20376</t>
+          <t>20303</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21416</t>
+          <t>22100</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43681</t>
+          <t>45401</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21802</t>
+          <t>21930</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7009</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23895</t>
+          <t>22925</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>902353</t>
+          <t>905606</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>991278</t>
+          <t>989497</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>750565</t>
+          <t>749087</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>804559</t>
+          <t>804365</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1672290</t>
+          <t>1667353</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1780456</t>
+          <t>1779671</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,74%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>412684</t>
+          <t>412508</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>491194</t>
+          <t>486650</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>146034</t>
+          <t>147116</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>195215</t>
+          <t>193432</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>572847</t>
+          <t>572741</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>662668</t>
+          <t>664860</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>340713</t>
+          <t>341730</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>408682</t>
+          <t>411617</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>40334</t>
+          <t>39795</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69288</t>
+          <t>69630</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>394420</t>
+          <t>395090</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>470872</t>
+          <t>471829</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>115460</t>
+          <t>113754</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>161627</t>
+          <t>158680</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>14949</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33435</t>
+          <t>33900</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>134714</t>
+          <t>135220</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>182895</t>
+          <t>183921</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a ruido tan alto que tiene que levantar la voz para hablar con otras personas en su trabajo en 2012</t>
+          <t>Población según la exposición a ruido tan alto que tiene que levantar la voz para hablar con otras personas en su trabajo en 2012 (tasa de respuesta: 99,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60575</t>
+          <t>61337</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88119</t>
+          <t>88281</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>70739</t>
+          <t>72613</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94574</t>
+          <t>94946</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>138583</t>
+          <t>139339</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>176820</t>
+          <t>176985</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,8%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36321</t>
+          <t>37067</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59697</t>
+          <t>59278</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25444</t>
+          <t>24990</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46017</t>
+          <t>45442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68541</t>
+          <t>68043</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98850</t>
+          <t>97703</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33381</t>
+          <t>33666</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56691</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5412</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19224</t>
+          <t>17936</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41829</t>
+          <t>41600</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>70937</t>
+          <t>69078</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9548</t>
+          <t>10139</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25149</t>
+          <t>26717</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18393</t>
+          <t>18044</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17924</t>
+          <t>18408</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38055</t>
+          <t>38021</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>351352</t>
+          <t>353751</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>414263</t>
+          <t>412596</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>321116</t>
+          <t>323487</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>371708</t>
+          <t>373581</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>687968</t>
+          <t>689425</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>765400</t>
+          <t>766133</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,51%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>255637</t>
+          <t>257730</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>315844</t>
+          <t>313350</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>139397</t>
+          <t>137432</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>183776</t>
+          <t>184765</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>408192</t>
+          <t>411208</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>481503</t>
+          <t>483125</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,48%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>149393</t>
+          <t>149380</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>195209</t>
+          <t>196344</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31779</t>
+          <t>32096</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56876</t>
+          <t>57430</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>189664</t>
+          <t>185887</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>246766</t>
+          <t>242636</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60250</t>
+          <t>60323</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>95893</t>
+          <t>98646</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13994</t>
+          <t>14200</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32225</t>
+          <t>32522</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>79679</t>
+          <t>78556</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>120455</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154639</t>
+          <t>158080</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>192791</t>
+          <t>196445</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>115556</t>
+          <t>115239</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>147488</t>
+          <t>147625</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>281700</t>
+          <t>281449</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>331643</t>
+          <t>332860</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,39%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77413</t>
+          <t>76545</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>111283</t>
+          <t>111015</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62471</t>
+          <t>62832</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>92876</t>
+          <t>91887</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>148507</t>
+          <t>149375</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>195316</t>
+          <t>196435</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,64%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25431</t>
+          <t>25453</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49472</t>
+          <t>50631</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>9474</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25976</t>
+          <t>26185</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38446</t>
+          <t>39280</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68950</t>
+          <t>68750</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20040</t>
+          <t>19923</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16744</t>
+          <t>15914</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12085</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32184</t>
+          <t>29994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>595396</t>
+          <t>592784</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>671317</t>
+          <t>671108</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>530566</t>
+          <t>530425</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>594269</t>
+          <t>591705</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1140140</t>
+          <t>1143328</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1245489</t>
+          <t>1243092</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,64%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>388363</t>
+          <t>389723</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>460058</t>
+          <t>461747</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>243854</t>
+          <t>244314</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>304574</t>
+          <t>303985</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>653878</t>
+          <t>653902</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>746387</t>
+          <t>745995</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,59%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>223749</t>
+          <t>225149</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>282700</t>
+          <t>282623</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>54174</t>
+          <t>55668</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>88506</t>
+          <t>87098</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>289255</t>
+          <t>291729</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>361313</t>
+          <t>356305</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84699</t>
+          <t>84147</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>125355</t>
+          <t>129571</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29904</t>
+          <t>30447</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56315</t>
+          <t>55671</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>123120</t>
+          <t>121263</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>172113</t>
+          <t>172885</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a ruido tan alto que tiene que levantar la voz para hablar con otras personas en su trabajo en 2016</t>
+          <t>Población según la exposición a ruido tan alto que tiene que levantar la voz para hablar con otras personas en su trabajo en 2016 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35159</t>
+          <t>35855</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58955</t>
+          <t>59564</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,47 +5762,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>43,4%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>38482</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>30964</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>46912</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>53,38%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>42,95%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>38482</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>29441</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>47390</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>53,38%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>40,84%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72011</t>
+          <t>71624</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100417</t>
+          <t>100249</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,89%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39786</t>
+          <t>38871</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63392</t>
+          <t>62337</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17818</t>
+          <t>18271</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33976</t>
+          <t>33821</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62988</t>
+          <t>61768</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90522</t>
+          <t>90859</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,4%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15100</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32870</t>
+          <t>33960</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>955</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8593</t>
+          <t>8776</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18499</t>
+          <t>19111</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37826</t>
+          <t>38692</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9782</t>
+          <t>9556</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25750</t>
+          <t>25540</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9141</t>
+          <t>9010</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12685</t>
+          <t>12157</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29902</t>
+          <t>29106</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>311428</t>
+          <t>312175</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>372010</t>
+          <t>372019</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>313656</t>
+          <t>315570</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>364823</t>
+          <t>365327</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>638909</t>
+          <t>642123</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>719423</t>
+          <t>721922</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,03%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>299910</t>
+          <t>298168</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>359437</t>
+          <t>358196</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>178261</t>
+          <t>180864</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>226654</t>
+          <t>229056</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>493716</t>
+          <t>496449</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>569866</t>
+          <t>571017</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,41%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>150135</t>
+          <t>151971</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>199517</t>
+          <t>202182</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62347</t>
+          <t>61272</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94623</t>
+          <t>94745</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>226417</t>
+          <t>224602</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>286155</t>
+          <t>285116</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59829</t>
+          <t>58222</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93665</t>
+          <t>93876</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19070</t>
+          <t>18374</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40404</t>
+          <t>39906</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>82471</t>
+          <t>83524</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>123599</t>
+          <t>123410</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>178614</t>
+          <t>180382</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>217603</t>
+          <t>218970</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>160876</t>
+          <t>162553</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>195464</t>
+          <t>196839</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>350300</t>
+          <t>352361</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>401175</t>
+          <t>404273</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,62%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79023</t>
+          <t>77468</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>113707</t>
+          <t>114036</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>63805</t>
+          <t>63271</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>95285</t>
+          <t>93928</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>151428</t>
+          <t>150253</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>195267</t>
+          <t>196008</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25482</t>
+          <t>26741</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50499</t>
+          <t>51800</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23189</t>
+          <t>23454</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44943</t>
+          <t>45789</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55619</t>
+          <t>53765</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86954</t>
+          <t>87857</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9375</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26072</t>
+          <t>26183</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11213</t>
+          <t>11355</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29981</t>
+          <t>29117</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24163</t>
+          <t>24258</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50851</t>
+          <t>48795</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>551512</t>
+          <t>548933</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>626942</t>
+          <t>626557</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>525942</t>
+          <t>527990</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>592562</t>
+          <t>590152</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1093780</t>
+          <t>1090961</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1196972</t>
+          <t>1191007</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>48,94%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>440150</t>
+          <t>434473</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>510584</t>
+          <t>511565</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>277771</t>
+          <t>277242</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>334710</t>
+          <t>336523</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>738947</t>
+          <t>736950</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>836133</t>
+          <t>826440</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>207781</t>
+          <t>207984</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>265088</t>
+          <t>264707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>94869</t>
+          <t>95082</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>134456</t>
+          <t>134710</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>316063</t>
+          <t>316696</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>386122</t>
+          <t>388260</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>87175</t>
+          <t>87363</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>129487</t>
+          <t>127941</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37600</t>
+          <t>37874</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67090</t>
+          <t>67990</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>133307</t>
+          <t>133112</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>185393</t>
+          <t>180012</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a ruido tan alto que tiene que levantar la voz para hablar con otras personas en su trabajo en 2023</t>
+          <t>Población según la exposición a ruido tan alto que tiene que levantar la voz para hablar con otras personas en su trabajo en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14796</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30707</t>
+          <t>30459</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15250</t>
+          <t>15916</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25270</t>
+          <t>25731</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33931</t>
+          <t>33748</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52818</t>
+          <t>53486</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>51,16%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22601</t>
+          <t>21959</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39022</t>
+          <t>38650</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12967</t>
+          <t>12191</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22818</t>
+          <t>21832</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38433</t>
+          <t>36968</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57295</t>
+          <t>57016</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,54%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19242</t>
+          <t>19229</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20263</t>
+          <t>20622</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,62 +8628,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2419</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1135</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>10041</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2419</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>9348</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>264268</t>
+          <t>265963</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>646495</t>
+          <t>654215</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>211545</t>
+          <t>212652</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>283842</t>
+          <t>285175</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>514486</t>
+          <t>517977</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>928384</t>
+          <t>961491</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>77,1%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110161</t>
+          <t>109746</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>395113</t>
+          <t>392459</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>118472</t>
+          <t>118739</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>174297</t>
+          <t>173634</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>237358</t>
+          <t>206195</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>535987</t>
+          <t>535148</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,91%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27051</t>
+          <t>26172</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>106422</t>
+          <t>108658</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21990</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44536</t>
+          <t>44411</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51838</t>
+          <t>52825</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135103</t>
+          <t>135775</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11571</t>
+          <t>12202</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57009</t>
+          <t>57360</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11253</t>
+          <t>12014</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28554</t>
+          <t>29312</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27494</t>
+          <t>25200</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>76172</t>
+          <t>74958</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>136042</t>
+          <t>135851</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>168984</t>
+          <t>169075</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111835</t>
+          <t>113198</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>136616</t>
+          <t>136727</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>256606</t>
+          <t>252854</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>296490</t>
+          <t>296559</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>67,23%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49711</t>
+          <t>50296</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>79052</t>
+          <t>79845</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44575</t>
+          <t>44806</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>67575</t>
+          <t>67234</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>102992</t>
+          <t>103031</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>139533</t>
+          <t>140438</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,84%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9474</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26077</t>
+          <t>26028</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13636</t>
+          <t>13596</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16490</t>
+          <t>16247</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34647</t>
+          <t>35593</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18107</t>
+          <t>17133</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16940</t>
+          <t>17418</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12464</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29884</t>
+          <t>29777</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>461627</t>
+          <t>460029</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>859387</t>
+          <t>836235</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>355537</t>
+          <t>357071</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>430236</t>
+          <t>440720</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>852887</t>
+          <t>846515</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1262701</t>
+          <t>1298402</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>72,42%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>187169</t>
+          <t>209091</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>474553</t>
+          <t>473559</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>186307</t>
+          <t>184475</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>248871</t>
+          <t>247729</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>389337</t>
+          <t>372122</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>695790</t>
+          <t>697193</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,89%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47174</t>
+          <t>46245</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>131947</t>
+          <t>133526</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30097</t>
+          <t>30195</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53647</t>
+          <t>54688</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>89871</t>
+          <t>87898</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>171796</t>
+          <t>174150</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21596</t>
+          <t>19935</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66016</t>
+          <t>65414</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20734</t>
+          <t>20777</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41396</t>
+          <t>41230</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45779</t>
+          <t>44478</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>97611</t>
+          <t>98339</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6601-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6601-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>143120</t>
+          <t>143173</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>182137</t>
+          <t>183421</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>96027</t>
+          <t>96185</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>119370</t>
+          <t>118475</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>245235</t>
+          <t>246973</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>295069</t>
+          <t>294424</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,67%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77021</t>
+          <t>75229</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>110362</t>
+          <t>109888</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17801</t>
+          <t>18674</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37650</t>
+          <t>37161</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100054</t>
+          <t>97321</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>141176</t>
+          <t>138448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>71804</t>
+          <t>69725</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>105862</t>
+          <t>104249</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21390</t>
+          <t>20521</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>82188</t>
+          <t>80950</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>119766</t>
+          <t>117642</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25352</t>
+          <t>25420</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49187</t>
+          <t>48322</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12265</t>
+          <t>12182</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30480</t>
+          <t>29789</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53908</t>
+          <t>55019</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>464226</t>
+          <t>463457</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>535363</t>
+          <t>532639</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>415390</t>
+          <t>414513</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>457190</t>
+          <t>458114</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>895169</t>
+          <t>893874</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>977059</t>
+          <t>978221</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,36%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>241956</t>
+          <t>239088</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>299002</t>
+          <t>298199</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82638</t>
+          <t>83060</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>120363</t>
+          <t>120573</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>337625</t>
+          <t>336773</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>408542</t>
+          <t>402982</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>243327</t>
+          <t>239323</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>300254</t>
+          <t>298916</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>21315</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40859</t>
+          <t>43595</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>268678</t>
+          <t>264135</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>330047</t>
+          <t>327703</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69403</t>
+          <t>69884</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>106903</t>
+          <t>107191</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>8636</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23796</t>
+          <t>24762</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>83384</t>
+          <t>83871</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>123083</t>
+          <t>125515</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>266815</t>
+          <t>264107</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>304324</t>
+          <t>302610</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>218901</t>
+          <t>219365</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>245787</t>
+          <t>246806</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>494427</t>
+          <t>496669</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>542351</t>
+          <t>541897</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,92%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71687</t>
+          <t>73289</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>105444</t>
+          <t>109252</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31228</t>
+          <t>32110</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56340</t>
+          <t>54750</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>109297</t>
+          <t>111331</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>153035</t>
+          <t>149854</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12394</t>
+          <t>13131</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31225</t>
+          <t>29880</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>6036</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20303</t>
+          <t>20495</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22100</t>
+          <t>22248</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45401</t>
+          <t>43810</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21930</t>
+          <t>21879</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6932</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22925</t>
+          <t>23386</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>905606</t>
+          <t>901890</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>989497</t>
+          <t>996542</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>749087</t>
+          <t>752301</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>804365</t>
+          <t>807122</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1667353</t>
+          <t>1669857</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1779671</t>
+          <t>1780441</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,77%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>412508</t>
+          <t>411167</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>486650</t>
+          <t>485374</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>147116</t>
+          <t>145802</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>193432</t>
+          <t>192637</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>572741</t>
+          <t>569504</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>664860</t>
+          <t>667938</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,8%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>341730</t>
+          <t>341459</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>411617</t>
+          <t>412057</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39795</t>
+          <t>40726</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69630</t>
+          <t>70374</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>395090</t>
+          <t>394576</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>471829</t>
+          <t>473440</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>113754</t>
+          <t>113374</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>158680</t>
+          <t>159975</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14949</t>
+          <t>15119</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33900</t>
+          <t>34220</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>135220</t>
+          <t>134765</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>183921</t>
+          <t>184590</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61337</t>
+          <t>60532</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88281</t>
+          <t>87872</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72613</t>
+          <t>72029</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94946</t>
+          <t>95358</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>139339</t>
+          <t>139437</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>176985</t>
+          <t>176128</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,53%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37067</t>
+          <t>36704</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59278</t>
+          <t>61210</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24990</t>
+          <t>25981</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45442</t>
+          <t>46574</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68043</t>
+          <t>66950</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97703</t>
+          <t>99266</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,74%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33666</t>
+          <t>34123</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>57159</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17936</t>
+          <t>19293</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41600</t>
+          <t>42948</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69078</t>
+          <t>71043</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10139</t>
+          <t>8897</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26717</t>
+          <t>25171</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18044</t>
+          <t>18523</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18408</t>
+          <t>17858</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38021</t>
+          <t>37894</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>353751</t>
+          <t>351579</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>412596</t>
+          <t>410842</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>323487</t>
+          <t>323082</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>373581</t>
+          <t>370054</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>689425</t>
+          <t>692586</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>766133</t>
+          <t>770504</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,8%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>257730</t>
+          <t>255868</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>313350</t>
+          <t>313262</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>137432</t>
+          <t>138844</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>184765</t>
+          <t>183862</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>411208</t>
+          <t>412289</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>483125</t>
+          <t>478465</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>149380</t>
+          <t>151058</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>196344</t>
+          <t>196985</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32096</t>
+          <t>31594</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57430</t>
+          <t>57595</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>185887</t>
+          <t>190039</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>242636</t>
+          <t>244751</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60323</t>
+          <t>60562</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>98646</t>
+          <t>94415</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14200</t>
+          <t>14019</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32522</t>
+          <t>32997</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>78556</t>
+          <t>80390</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120455</t>
+          <t>121393</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>158080</t>
+          <t>157025</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>196445</t>
+          <t>194475</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>115239</t>
+          <t>114714</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>147625</t>
+          <t>147267</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>281449</t>
+          <t>281171</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>332860</t>
+          <t>330573</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>59,98%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>76545</t>
+          <t>76716</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>111015</t>
+          <t>111573</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62832</t>
+          <t>62766</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>91887</t>
+          <t>93426</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>149375</t>
+          <t>149530</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>196435</t>
+          <t>196575</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,67%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25453</t>
+          <t>26213</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50631</t>
+          <t>49203</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9474</t>
+          <t>10391</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26185</t>
+          <t>27616</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39280</t>
+          <t>39172</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68750</t>
+          <t>68878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19923</t>
+          <t>20256</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15914</t>
+          <t>16441</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12085</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29994</t>
+          <t>31348</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>592784</t>
+          <t>591777</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>671108</t>
+          <t>669195</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>530425</t>
+          <t>533058</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>591705</t>
+          <t>593633</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1143328</t>
+          <t>1145175</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1243092</t>
+          <t>1242496</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,61%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>389723</t>
+          <t>393070</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>461747</t>
+          <t>462868</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>244314</t>
+          <t>246156</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>303985</t>
+          <t>302109</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>653902</t>
+          <t>655148</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>745995</t>
+          <t>743243</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,47%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>225149</t>
+          <t>221665</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>282623</t>
+          <t>280648</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>55668</t>
+          <t>54072</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>87098</t>
+          <t>87307</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>291729</t>
+          <t>290255</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>356305</t>
+          <t>357799</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84147</t>
+          <t>85020</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>129571</t>
+          <t>127489</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30447</t>
+          <t>30165</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55671</t>
+          <t>56486</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121263</t>
+          <t>122466</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>172885</t>
+          <t>172092</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35855</t>
+          <t>36235</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59564</t>
+          <t>58660</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30964</t>
+          <t>31277</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46912</t>
+          <t>47749</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71624</t>
+          <t>72323</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100249</t>
+          <t>100790</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,15%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38871</t>
+          <t>39092</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62337</t>
+          <t>62451</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18271</t>
+          <t>17646</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33821</t>
+          <t>33661</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61768</t>
+          <t>63227</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90859</t>
+          <t>91843</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>15614</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33960</t>
+          <t>33405</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>951</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8776</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19111</t>
+          <t>18274</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>37866</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9556</t>
+          <t>9762</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25540</t>
+          <t>24658</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9010</t>
+          <t>9488</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>12595</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29106</t>
+          <t>31049</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>312175</t>
+          <t>310358</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>372019</t>
+          <t>369980</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>315570</t>
+          <t>312628</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>365327</t>
+          <t>365518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>642123</t>
+          <t>641759</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>721922</t>
+          <t>720030</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>45,91%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>298168</t>
+          <t>301666</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>358196</t>
+          <t>361120</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>180864</t>
+          <t>181546</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>229056</t>
+          <t>228543</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>496449</t>
+          <t>497837</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>571017</t>
+          <t>571715</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151971</t>
+          <t>151157</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>202182</t>
+          <t>198912</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61272</t>
+          <t>60438</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94745</t>
+          <t>94194</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>224602</t>
+          <t>225945</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>285116</t>
+          <t>282419</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>58222</t>
+          <t>58810</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93876</t>
+          <t>91095</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18374</t>
+          <t>19216</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39906</t>
+          <t>40210</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>83524</t>
+          <t>83310</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>123410</t>
+          <t>124358</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>180382</t>
+          <t>181481</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>218970</t>
+          <t>220526</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>162553</t>
+          <t>162009</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>196839</t>
+          <t>196946</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>352361</t>
+          <t>351659</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>404273</t>
+          <t>403860</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>61,56%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77468</t>
+          <t>78451</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>114036</t>
+          <t>111865</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>63271</t>
+          <t>63350</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>93928</t>
+          <t>93473</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>150253</t>
+          <t>149615</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>196008</t>
+          <t>197460</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,1%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26741</t>
+          <t>26367</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51800</t>
+          <t>50205</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23454</t>
+          <t>23673</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45789</t>
+          <t>44760</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53765</t>
+          <t>53566</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87857</t>
+          <t>86303</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9020</t>
+          <t>9597</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26183</t>
+          <t>26092</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11355</t>
+          <t>10608</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29117</t>
+          <t>28906</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24258</t>
+          <t>23737</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48795</t>
+          <t>49355</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>548933</t>
+          <t>551792</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>626557</t>
+          <t>628226</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>527990</t>
+          <t>526036</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>590152</t>
+          <t>587842</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1090961</t>
+          <t>1095081</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1191007</t>
+          <t>1196197</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>49,15%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>434473</t>
+          <t>440202</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>511565</t>
+          <t>513176</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>277242</t>
+          <t>279731</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>336523</t>
+          <t>337535</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>736950</t>
+          <t>732846</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>826440</t>
+          <t>831306</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>207984</t>
+          <t>208872</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>264707</t>
+          <t>265898</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>95082</t>
+          <t>94238</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>134710</t>
+          <t>134694</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>316696</t>
+          <t>314092</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>388260</t>
+          <t>386931</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>87363</t>
+          <t>87268</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>127941</t>
+          <t>128731</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37874</t>
+          <t>36688</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67990</t>
+          <t>66119</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>133112</t>
+          <t>133133</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>180012</t>
+          <t>179395</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -8249,32 +8249,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22237</t>
+          <t>31313</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>21206</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30459</t>
+          <t>43444</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,32 +8284,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20564</t>
+          <t>22455</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15916</t>
+          <t>16739</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25731</t>
+          <t>28187</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>42802</t>
+          <t>53767</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33748</t>
+          <t>42466</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53486</t>
+          <t>66086</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>49,27%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30031</t>
+          <t>39765</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21959</t>
+          <t>29538</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38650</t>
+          <t>49965</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,32 +8397,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17307</t>
+          <t>22406</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12191</t>
+          <t>16390</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21832</t>
+          <t>28179</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>47338</t>
+          <t>62171</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36968</t>
+          <t>49512</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57016</t>
+          <t>74699</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>55,69%</t>
         </is>
       </c>
     </row>
@@ -8475,32 +8475,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10726</t>
+          <t>14309</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>8561</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19229</t>
+          <t>24584</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11978</t>
+          <t>15624</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>9237</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20622</t>
+          <t>25210</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7531</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10041</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>87953</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>87953</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>87953</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>134129</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>134129</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>134129</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,32 +8818,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>436691</t>
+          <t>215530</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>265963</t>
+          <t>188711</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>654215</t>
+          <t>241565</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,32 +8853,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>238004</t>
+          <t>231048</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>212652</t>
+          <t>212947</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>285175</t>
+          <t>250859</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>674695</t>
+          <t>446577</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>517977</t>
+          <t>414145</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>961491</t>
+          <t>479558</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>44,58%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>265544</t>
+          <t>287670</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>109746</t>
+          <t>260593</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>392459</t>
+          <t>315083</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>152613</t>
+          <t>164842</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>118739</t>
+          <t>147134</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>173634</t>
+          <t>183501</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>418157</t>
+          <t>452512</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>206195</t>
+          <t>420955</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>535148</t>
+          <t>484191</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>45,01%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69357</t>
+          <t>78390</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26172</t>
+          <t>58999</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108658</t>
+          <t>97411</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31903</t>
+          <t>36630</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>26781</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44411</t>
+          <t>49698</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>101260</t>
+          <t>115020</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52825</t>
+          <t>95104</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135775</t>
+          <t>141158</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33770</t>
+          <t>39389</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12202</t>
+          <t>26737</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57360</t>
+          <t>57218</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19235</t>
+          <t>22199</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12014</t>
+          <t>14135</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29312</t>
+          <t>33812</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>53005</t>
+          <t>61588</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25200</t>
+          <t>45262</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>74958</t>
+          <t>79597</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>805362</t>
+          <t>620979</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>805362</t>
+          <t>620979</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>805362</t>
+          <t>620979</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>441755</t>
+          <t>454719</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>441755</t>
+          <t>454719</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>441755</t>
+          <t>454719</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1247117</t>
+          <t>1075698</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1247117</t>
+          <t>1075698</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1247117</t>
+          <t>1075698</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9387,32 +9387,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>152467</t>
+          <t>171985</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>135851</t>
+          <t>154201</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>169075</t>
+          <t>188531</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9422,32 +9422,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>125220</t>
+          <t>133978</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113198</t>
+          <t>120864</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>136727</t>
+          <t>146894</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9457,32 +9457,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>277687</t>
+          <t>305963</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>252854</t>
+          <t>283224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>296559</t>
+          <t>326229</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>66,9%</t>
         </is>
       </c>
     </row>
@@ -9500,32 +9500,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64568</t>
+          <t>69804</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>50296</t>
+          <t>56128</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>79845</t>
+          <t>85723</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9535,32 +9535,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>54884</t>
+          <t>63187</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44806</t>
+          <t>50756</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>67234</t>
+          <t>75359</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>119452</t>
+          <t>132991</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>103031</t>
+          <t>114427</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>140438</t>
+          <t>152416</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,26%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>16613</t>
+          <t>17467</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10055</t>
+          <t>10494</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26028</t>
+          <t>28261</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,32 +9648,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8010</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13596</t>
+          <t>16746</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>24623</t>
+          <t>27881</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16247</t>
+          <t>18658</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35593</t>
+          <t>39132</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -9726,32 +9726,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8411</t>
+          <t>8878</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17133</t>
+          <t>18417</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10952</t>
+          <t>11903</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17418</t>
+          <t>18536</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>19363</t>
+          <t>20781</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29777</t>
+          <t>32410</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>242059</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>242059</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>242059</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>199066</t>
+          <t>219483</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>199066</t>
+          <t>219483</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>199066</t>
+          <t>219483</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>441125</t>
+          <t>487617</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>441125</t>
+          <t>487617</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>441125</t>
+          <t>487617</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>611395</t>
+          <t>418827</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>460029</t>
+          <t>384477</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>836235</t>
+          <t>452673</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>383789</t>
+          <t>387480</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>357071</t>
+          <t>364753</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>440720</t>
+          <t>410496</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>995184</t>
+          <t>806308</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>846515</t>
+          <t>763879</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1298402</t>
+          <t>847401</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>49,92%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>360143</t>
+          <t>397239</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>209091</t>
+          <t>363978</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>473559</t>
+          <t>430263</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>224803</t>
+          <t>250436</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>184475</t>
+          <t>229459</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247729</t>
+          <t>272845</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>584946</t>
+          <t>647674</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>372122</t>
+          <t>608334</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>697193</t>
+          <t>691353</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>40,73%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>96697</t>
+          <t>110165</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46245</t>
+          <t>90637</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>133526</t>
+          <t>132954</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>41164</t>
+          <t>48360</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30195</t>
+          <t>36637</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>54688</t>
+          <t>63803</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137861</t>
+          <t>158525</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>87898</t>
+          <t>135361</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>174150</t>
+          <t>184409</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>44600</t>
+          <t>50835</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19935</t>
+          <t>36348</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>70386</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>30188</t>
+          <t>34102</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20777</t>
+          <t>24379</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41230</t>
+          <t>47048</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>74788</t>
+          <t>84937</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44478</t>
+          <t>66699</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>98339</t>
+          <t>108410</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1112835</t>
+          <t>977066</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1112835</t>
+          <t>977066</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1112835</t>
+          <t>977066</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1792779</t>
+          <t>1697444</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1792779</t>
+          <t>1697444</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1792779</t>
+          <t>1697444</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
